--- a/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Triphammer_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Performance Food/Performance Food_Triphammer_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,6 +674,1014 @@
         <v>23.87</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TN330</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Natalie's - Honey Tangerine</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="E13" t="n">
+        <v>14.57</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AH252</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Juice</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TN454</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Mango</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TN362</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Natalie's - Orange Pineapple</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="E16" t="n">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TN380</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Natalie's - Strawberry Lemonade</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11.31</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FK824</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Anchovies</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>68.23999999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>68.23999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MM818</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Balsamic Glaze</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="E19" t="n">
+        <v>82.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>J3088</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Base - Chicken (No MSG)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="E20" t="n">
+        <v>124.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>K1570</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Buttermilk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="E21" t="n">
+        <v>17.17</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15168</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Can - Black Bean</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="E22" t="n">
+        <v>106.98</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>33808</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Eggplant - Fresh</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NH166</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lettuce - Arcadian Blend</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>138.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HB334</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Onion - Red Fresh Whole Peeled</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="E25" t="n">
+        <v>128.88</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>K7616</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Onion - Yellow (peeled)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="E26" t="n">
+        <v>102.06</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BR632</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cantaloupe - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="E27" t="n">
+        <v>161.96</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VR126</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cheddar - Extra Sharp White</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ABK44</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chicken Tenders - (1oz)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="E29" t="n">
+        <v>45.62</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CF096</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fresh Mozz (Sliced)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="E30" t="n">
+        <v>100.38</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>FN108</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mango - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>30.81</v>
+      </c>
+      <c r="E31" t="n">
+        <v>184.86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>28666</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Maple Syrup (Blend)</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>46.58</v>
+      </c>
+      <c r="E32" t="n">
+        <v>46.58</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BR628</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pineapple - Fresh (Chunk)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="E33" t="n">
+        <v>127.74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>FA300</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sundried Tomatoes</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24.61</v>
+      </c>
+      <c r="E34" t="n">
+        <v>73.83</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>F6472</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Vinegar - Balsamic</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>36.98</v>
+      </c>
+      <c r="E35" t="n">
+        <v>36.98</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>LF010</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Base - Vegetable</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>12798</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Can - Cranberry Sauce - Jellied</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>68.63</v>
+      </c>
+      <c r="E37" t="n">
+        <v>68.63</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>81692</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Can - Garbanzo Beans</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="E38" t="n">
+        <v>62.06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10600</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Can - Great Northern Bean</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>36.09</v>
+      </c>
+      <c r="E39" t="n">
+        <v>144.36</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10198</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Capers</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>65.23999999999999</v>
+      </c>
+      <c r="E40" t="n">
+        <v>65.23999999999999</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GC902</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Chicken Breast - Random</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>92.67</v>
+      </c>
+      <c r="E41" t="n">
+        <v>278.01</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CG686</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Chicken Breast - Retail (Cooked)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>30</v>
+      </c>
+      <c r="D42" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1641.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>V8852</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Chicken Filet - Breaded 4 oz (Raw)</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="E43" t="n">
+        <v>195.12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ABK40</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Chicken Wing - Fully Cooked</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>142.58</v>
+      </c>
+      <c r="E44" t="n">
+        <v>142.58</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WF580</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Corned Beef (Sliced)</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>66.26000000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>198.78</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>71210</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cream Cheese</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>10</v>
+      </c>
+      <c r="D46" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CP992</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Fries - Steak</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="E47" t="n">
+        <v>87.78</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P5596</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Haddock Fillet - Battered (frz)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>101.46</v>
+      </c>
+      <c r="E48" t="n">
+        <v>202.92</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HH264</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Muenster (Sliced)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="E49" t="n">
+        <v>96.14</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>E3556</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pastrami (Sliced)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="E50" t="n">
+        <v>199.35</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RC608</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PKT Sour Cream</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="E51" t="n">
+        <v>33.58</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>FD046</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Potsticker - Chicken Lemongrass</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="E52" t="n">
+        <v>81.31999999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>36776</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Prosciutto</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>62.48</v>
+      </c>
+      <c r="E53" t="n">
+        <v>124.96</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NH016</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Provolone (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="E54" t="n">
+        <v>309.96</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>83632</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Roast Beef (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>126.08</v>
+      </c>
+      <c r="E55" t="n">
+        <v>378.24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>38476</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Salami (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="E56" t="n">
+        <v>93.59999999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PW962</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Smoked Turkey (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="E57" t="n">
+        <v>641.34</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AV906</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Swiss (Sliced)</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>57.13</v>
+      </c>
+      <c r="E58" t="n">
+        <v>114.26</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DT820</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Turkey (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>15</v>
+      </c>
+      <c r="D59" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E59" t="n">
+        <v>715.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>NG746</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Wrap - Garlic Herb (12')</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="E60" t="n">
+        <v>29.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
